--- a/test/fixtures/roster.xlsx
+++ b/test/fixtures/roster.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1093,6 +1093,77 @@
         <v>50</v>
       </c>
       <c r="V9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1003</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>正職員</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>正職員</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>一般行政職</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>菅野　豊</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>24414</v>
+      </c>
+      <c r="K10" t="n">
+        <v>40269</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1700</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2100</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>農業委員会</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>700</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>主事</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>1700010</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>事務局</t>
+        </is>
+      </c>
+      <c r="U10" t="n">
+        <v>50</v>
+      </c>
+      <c r="V10" t="n">
         <v>1</v>
       </c>
     </row>
